--- a/diseases/d163/2026-2029.xlsx
+++ b/diseases/d163/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>2</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.03537951651591013</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>41</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.3831400975596171</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>26</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.242966891135367</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>16</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.1495180868525335</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -3537,9 +3516,6 @@
       <c r="O16" t="n">
         <v>15</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.1401732064242502</v>
       </c>
@@ -3933,9 +3909,6 @@
       <c r="O18" t="n">
         <v>1</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -4329,9 +4302,6 @@
       <c r="O20" t="n">
         <v>16</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.1495180868525335</v>
       </c>
@@ -4725,9 +4695,6 @@
       <c r="O22" t="n">
         <v>2</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.03537951651591013</v>
       </c>
@@ -5121,9 +5088,6 @@
       <c r="O24" t="n">
         <v>10</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.09344880428283346</v>
       </c>
@@ -5517,9 +5481,6 @@
       <c r="O26" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -5913,9 +5874,6 @@
       <c r="O28" t="n">
         <v>10</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.09344880428283346</v>
       </c>
@@ -6304,16 +6262,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -6466,10 +6421,10 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -6811,7 +6766,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d163/2026-2029.xlsx
+++ b/diseases/d163/2026-2029.xlsx
@@ -29303,6 +29303,399 @@
         </is>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>hantavirus-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>汉他病毒出血热</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_402_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_402_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>hantavirus-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>汉他病毒出血热</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_402_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_402_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>Nephropathia epidemica</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS renal hantavirus syndrome category.</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN151" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP151" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_402_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV151" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA151" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29336,7 +29729,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -29419,7 +29812,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
@@ -29429,7 +29822,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -29449,7 +29842,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13">
